--- a/FLOOR.xlsx
+++ b/FLOOR.xlsx
@@ -19,7 +19,7 @@
     <t>20104133</t>
   </si>
   <si>
-    <t>DK SNACK ASORTED 12S</t>
+    <t>DK SNACK ASORTED</t>
   </si>
   <si>
     <t>FLOOR</t>
